--- a/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
+++ b/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
@@ -22,20 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="9"/>
-        <x:color theme="1"/>
-        <x:rFont val="游ゴシック Light"/>
-        <x:family val="3"/>
-        <x:charset val="128"/>
-        <x:scheme val="major"/>
-      </x:rPr>
-      <x:t xml:space="preserve">
+    <x:t xml:space="preserve">
 漢字
 </x:t>
-    </x:r>
     <x:rPh sb="1" eb="3">
       <x:t>カンジ</x:t>
     </x:rPh>
